--- a/Estimated_Tax_Calculator_FedOnly.xlsx
+++ b/Estimated_Tax_Calculator_FedOnly.xlsx
@@ -595,7 +595,7 @@
       <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Quick Start Guide</t>
         </is>
@@ -623,7 +623,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Step 4: (Optional) Enter your estimated 'Itemized Deductions' if you expect to exceed the Standard Deduction.</t>
         </is>
@@ -640,7 +640,7 @@
       <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Important Notes</t>
         </is>

--- a/Estimated_Tax_Calculator_FedOnly.xlsx
+++ b/Estimated_Tax_Calculator_FedOnly.xlsx
@@ -261,6 +261,11 @@
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
         <t>Warns if Head of Household is selected with zero dependents (legal but rare).</t>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0">
+      <text>
+        <t>Flags if you have stale records from previous quarters which will artificially warp your pro-ration math.</t>
       </text>
     </comment>
   </commentList>
@@ -984,7 +989,7 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>IF(MAX('Wage Snapshots'!A:A)=0, 0, (SUM('Wage Snapshots'!B:B) / MAX(1, MAX('Wage Snapshots'!A:A) - DATE(B8,1,1))) * (DATE(B8,12,31) - MAX('Wage Snapshots'!A:A)))</f>
+        <f>IF(MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0")=0, 0, (SUM('Wage Snapshots'!C:C) / MAX(1, MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0") - DATE(B8,1,1))) * (DATE(B8,12,31) - MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0")))</f>
         <v/>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -1001,7 +1006,7 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>IF(MAX('Wage Snapshots'!A:A)=0, 0, (SUM('Wage Snapshots'!C:D) / MAX(1, MAX('Wage Snapshots'!A:A) - DATE(B8,1,1))) * (DATE(B8,12,31) - MAX('Wage Snapshots'!A:A)))</f>
+        <f>IF(MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0")=0, 0, (SUM('Wage Snapshots'!D:E) / MAX(1, MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0") - DATE(B8,1,1))) * (DATE(B8,12,31) - MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0")))</f>
         <v/>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1060,7 +1065,7 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>SUM('Wage Snapshots'!B:B) + (B15 * B14) + B13</f>
+        <f>SUM('Wage Snapshots'!C:C) + (B15 * B14) + B13</f>
         <v/>
       </c>
       <c r="D20" s="2" t="n"/>
@@ -1081,7 +1086,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>B20 - SUM('Wage Snapshots'!C:D) - (B16 * B14)</f>
+        <f>B20 - SUM('Wage Snapshots'!D:E) - (B16 * B14)</f>
         <v/>
       </c>
       <c r="D21" s="2" t="n"/>
@@ -1176,7 +1181,7 @@
         </is>
       </c>
       <c r="J27">
-        <f>IF(OR(MAX('Wage Snapshots'!A:A)=0, (B9 - MAX('Wage Snapshots'!A:A)) &gt; 30), "🔴 !!! 30+ DAYS OLD !!!", "OK")</f>
+        <f>IF(OR(MAX('Wage Snapshots'!B:B)=0, (B9 - MAX('Wage Snapshots'!B:B)) &gt; 30), "🔴 !!! 30+ DAYS OLD !!!", "OK")</f>
         <v/>
       </c>
     </row>
@@ -1284,7 +1289,15 @@
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="15" t="n"/>
       <c r="D34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Stale Income Data:</t>
+        </is>
+      </c>
+      <c r="J34">
+        <f>IF(AND(MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0")&gt;0, ROUNDUP(MONTH(MINIFS('Wage Snapshots'!B:B, 'Wage Snapshots'!B:B, "&gt;0"))/3, 0) &lt; B10), "⚠️ WAGES FROM PRIOR QTR", IF(OR(AND(B10&gt;1, COUNTIF('Investment Income Snapshots'!A:A, "*Q1*")&gt;0), AND(B10&gt;2, COUNTIF('Investment Income Snapshots'!A:A, "*Q2*")&gt;0), AND(B10&gt;3, COUNTIF('Investment Income Snapshots'!A:A, "*Q3*")&gt;0)), "⚠️ INV. INCOME FROM PRIOR QTR", "OK"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" hidden="1">
       <c r="A35" s="2" t="n"/>
@@ -1339,7 +1352,7 @@
         </is>
       </c>
       <c r="B42" s="15">
-        <f>XLOOKUP(B2, 'Tax Constants'!B88:B91, 'Tax Constants'!C88:C91, 200000)</f>
+        <f>XLOOKUP(B2, 'Tax Constants'!B49:B52, 'Tax Constants'!C49:C52, 200000)</f>
         <v/>
       </c>
       <c r="D42" s="2" t="n"/>
@@ -1365,7 +1378,7 @@
         </is>
       </c>
       <c r="B44" s="15">
-        <f>XLOOKUP(B2, 'Tax Constants'!B88:B91, 'Tax Constants'!D88:D91, 200000)</f>
+        <f>XLOOKUP(B2, 'Tax Constants'!B49:B52, 'Tax Constants'!D49:D52, 200000)</f>
         <v/>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -1391,7 +1404,7 @@
         </is>
       </c>
       <c r="B46" s="15">
-        <f>XLOOKUP(B2, 'Tax Constants'!B88:B91, 'Tax Constants'!E88:E91, 200000)</f>
+        <f>XLOOKUP(B2, 'Tax Constants'!B49:B52, 'Tax Constants'!E49:E52, 200000)</f>
         <v/>
       </c>
       <c r="D46" s="2" t="n"/>
@@ -1459,7 +1472,7 @@
         </is>
       </c>
       <c r="B52" s="15">
-        <f>SUM('Wage Snapshots'!E:E) + SUMIFS(F3:F10, G3:G10, "Fed*")</f>
+        <f>SUM('Wage Snapshots'!F:F) + SUMIFS(F3:F10, G3:G10, "Fed*")</f>
         <v/>
       </c>
       <c r="D52" s="2" t="n"/>
@@ -1634,52 +1647,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col hidden="1" width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col hidden="1" width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Employer / Source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Gross W-2 Income</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Pre-tax Deductions</t>
+          <t>Gross W-2 Income (YTD)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>HSA Contributions</t>
+          <t>Pre-tax Deductions (YTD)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Fed Tax Withheld</t>
+          <t>HSA Contributions (YTD)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CA Tax Withheld</t>
+          <t>Fed Tax Withheld (YTD)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>FICA/Med/SDI</t>
+          <t>CA Tax Withheld (YTD)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FICA/Med/SDI (YTD)</t>
         </is>
       </c>
     </row>
@@ -2748,9 +2767,10 @@
 ---
 # Schema 1: Wage Snapshots (Paystubs)
 If the document is a paystub, RSU release confirmation, or W-2 income event, extract the data into the following columns exactly as defined:
-| Date | Gross W-2 Income | Pre-tax Deductions | HSA Contributions | Fed Tax Withheld | CA Tax Withheld | FICA/Med/SDI |
+| Employer / Source | Date | Gross W-2 Income | Pre-tax Deductions | HSA Contributions | Fed Tax Withheld | CA Tax Withheld | FICA/Med/SDI |
 |---|---|---|---|---|---|---|
 **Extraction Logic for Wage Snapshots:**
+*   **Employer / Source**: The name of the employer or source of income (e.g., `Google`, `Acme Corp`, `Spouse W-2`). If not clearly inferrable from the document, leave this field blank.
 *   **Date**: The date of the paystub or vest event (Format: MM/DD/YYYY).
 *   **Gross W-2 Income**: The **Year-to-Date (YTD)** gross pay, combining base salary, bonus payout, and/or the total taxable value of RSU vests up to this date.
 *   **Pre-tax Deductions**: The sum of all **YTD** pre-tax deductions (e.g., Traditional 401k, FSA, Health/Dental/Vision premiums). **CRITICAL IMPERATIVE**: Do **not** include HSA contributions in this sum.
